--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -183,7 +183,109 @@
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">product</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">objective</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">period</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">year</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">startDate</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">endDate</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">createdBy</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">createdAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260819-073228-B8679789</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین شهریور ماه 1405</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pro</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jazb</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shahrivar</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-23</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19T07:32:28.290Z</t>
         </is>
       </c>
     </row>
@@ -997,7 +1099,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T06:39:09.362925+00:00</t>
+          <t xml:space="preserve">2026-08-19T07:32:36.163154+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -1039,7 +1039,79 @@
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">contentTypeId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">version</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">createdBy</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">createdAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-BANNER</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19T07:34:28.874Z</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1171,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T07:32:36.163154+00:00</t>
+          <t xml:space="preserve">2026-08-19T07:34:40.345368+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -158,6 +158,118 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260819-073228-B8679789</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین شهریور ماه 1405</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referral</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">referral</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مدیر اصلی</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1171,7 +1283,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T07:34:40.345368+00:00</t>
+          <t xml:space="preserve">2026-08-19T07:35:02.943892+00:00</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1295,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1307,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -261,7 +261,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t xml:space="preserve">deleted</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T07:35:02.943892+00:00</t>
+          <t xml:space="preserve">2026-08-19T07:37:43.223880+00:00</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -338,6 +338,16 @@
           <t xml:space="preserve">createdAt</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">deletedAt</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">deletedBy</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -387,7 +397,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t xml:space="preserve">deleted</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -398,6 +408,16 @@
       <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:32:28.290Z</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19T09:31:20.257Z</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
     </row>
@@ -1179,6 +1199,16 @@
           <t xml:space="preserve">createdAt</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">deletedAt</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">deletedBy</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1213,7 +1243,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t xml:space="preserve">deleted</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1224,6 +1254,16 @@
       <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:28.874Z</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19T09:31:30.138Z</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1323,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T07:37:43.223880+00:00</t>
+          <t xml:space="preserve">2026-08-19T09:31:31.285615+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -1267,6 +1267,63 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-TEXT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:00:46.438Z</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1323,7 +1380,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T09:31:31.285615+00:00</t>
+          <t xml:space="preserve">2026-08-25T04:00:53.687835+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -421,6 +421,78 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">challenges_cost</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ever</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-08-25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:04:35.739Z</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1380,7 +1452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:00:53.687835+00:00</t>
+          <t xml:space="preserve">2026-08-25T04:04:42.956209+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -955,6 +955,38 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-260825-040705-7B535FCC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:05.239Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1452,7 +1484,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:04:42.956209+00:00</t>
+          <t xml:space="preserve">2026-08-25T04:07:13.723804+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -756,6 +756,38 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260825-040736-7A5989EB</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:36.116Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1484,7 +1516,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:13.723804+00:00</t>
+          <t xml:space="preserve">2026-08-25T04:07:45.403364+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,110 +161,222 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1516,7 +1628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:45.403364+00:00</t>
+          <t xml:space="preserve">2026-08-25T04:07:58.123727+00:00</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1640,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1652,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,7 +161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -226,12 +226,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,110 +273,222 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1628,7 +1740,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:58.123727+00:00</t>
+          <t xml:space="preserve">2026-08-25T04:18:31.972055+00:00</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1752,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1764,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,7 +161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -181,24 +181,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -226,12 +226,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,7 +273,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -338,12 +338,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,110 +385,222 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1740,7 +1852,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:31.972055+00:00</t>
+          <t xml:space="preserve">2026-08-25T04:29:08.697496+00:00</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1864,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1876,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -829,6 +829,78 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shahrivar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-08-25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T08:46:30.212Z</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1852,7 +1924,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:08.697496+00:00</t>
+          <t xml:space="preserve">2026-08-25T08:46:40.356710+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -1427,6 +1427,38 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-260825-084708-CE8E74A3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T08:47:08.459Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1924,7 +1956,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:46:40.356710+00:00</t>
+          <t xml:space="preserve">2026-08-25T08:47:17.185433+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -1196,6 +1196,38 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260825-084745-DB702A58</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عصر قلم</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T08:47:45.138Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1956,7 +1988,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:47:17.185433+00:00</t>
+          <t xml:space="preserve">2026-08-25T08:47:55.089889+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -1932,6 +1932,63 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-TEXT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T08:48:09.167Z</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1988,7 +2045,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:47:55.089889+00:00</t>
+          <t xml:space="preserve">2026-08-25T08:48:16.415189+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,57 +161,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -226,17 +226,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,7 +273,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -293,24 +293,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -338,12 +338,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,7 +385,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -450,12 +450,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,110 +497,222 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2045,7 +2157,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:16.415189+00:00</t>
+          <t xml:space="preserve">2026-08-25T08:48:51.370303+00:00</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2169,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2181,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,7 +161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -226,12 +226,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,57 +273,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -338,17 +338,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,7 +385,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -405,24 +405,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -450,12 +450,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,110 +609,222 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2157,7 +2269,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:51.370303+00:00</t>
+          <t xml:space="preserve">2026-08-25T08:49:46.831917+00:00</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2281,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2293,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,7 +161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -226,12 +226,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,7 +273,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -338,12 +338,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,57 +385,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -450,17 +450,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -517,24 +517,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -562,12 +562,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,110 +721,222 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2269,7 +2381,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:46.831917+00:00</t>
+          <t xml:space="preserve">2026-08-25T08:50:35.683281+00:00</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2393,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2405,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -1237,6 +1237,78 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">w1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iran_broker_topic</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shahrivar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-31</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T09:15:40.433Z</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2381,7 +2453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:35.683281+00:00</t>
+          <t xml:space="preserve">2026-08-25T09:15:49.804438+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -1899,6 +1899,38 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-260825-091629-42946251</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایران بروکر</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">topic</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T09:16:29.232Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2453,7 +2485,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:15:49.804438+00:00</t>
+          <t xml:space="preserve">2026-08-25T09:16:37.043907+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,57 +161,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -226,12 +226,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,7 +273,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -338,12 +338,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,7 +385,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -450,12 +450,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,57 +497,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -562,17 +562,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -629,24 +629,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -674,12 +674,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,110 +833,222 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2429,6 +2541,63 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-TEXT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T09:16:51.281Z</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2485,7 +2654,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:37.043907+00:00</t>
+          <t xml:space="preserve">2026-08-25T09:16:58.380179+00:00</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2666,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2678,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -1421,6 +1421,78 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shahrivar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:14:24.592Z</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2654,7 +2726,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:58.380179+00:00</t>
+          <t xml:space="preserve">2026-08-25T10:14:32.188734+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -1820,6 +1820,38 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260825-101513-C38B013A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:15:13.819Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2726,7 +2758,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:14:32.188734+00:00</t>
+          <t xml:space="preserve">2026-08-25T10:15:23.351789+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2147,6 +2147,38 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-260825-101544-73583EE0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:15:44.932Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2758,7 +2790,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:15:23.351789+00:00</t>
+          <t xml:space="preserve">2026-08-25T10:15:54.850098+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2734,6 +2734,63 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-TEXT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:16:25.255Z</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2790,7 +2847,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:15:54.850098+00:00</t>
+          <t xml:space="preserve">2026-08-25T10:16:33.931727+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,57 +161,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -226,12 +226,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,57 +273,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -338,12 +338,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,7 +385,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -450,12 +450,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,57 +609,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -674,17 +674,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -786,12 +786,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,110 +945,222 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2847,7 +2959,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:16:33.931727+00:00</t>
+          <t xml:space="preserve">2026-08-25T10:17:16.067993+00:00</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2971,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2983,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,7 +161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -226,12 +226,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,57 +273,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -338,12 +338,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,57 +385,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -450,12 +450,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,57 +721,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -853,24 +853,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -898,12 +898,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,110 +1057,222 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2959,7 +3071,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:16.067993+00:00</t>
+          <t xml:space="preserve">2026-08-25T10:19:29.873672+00:00</t>
         </is>
       </c>
     </row>
@@ -2971,7 +3083,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>
@@ -2983,7 +3095,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,7 +161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -226,12 +226,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,7 +273,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -338,12 +338,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,57 +385,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -450,12 +450,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,57 +497,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,57 +833,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -898,17 +898,17 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -965,24 +965,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1169,110 +1169,222 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3071,7 +3183,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:29.873672+00:00</t>
+          <t xml:space="preserve">2026-08-25T10:22:51.480792+00:00</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3195,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3207,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,7 +161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -226,12 +226,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,7 +273,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -338,12 +338,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,7 +385,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -450,12 +450,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,57 +497,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,57 +609,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,57 +945,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1010,17 +1010,17 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1077,24 +1077,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1281,110 +1281,222 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3183,7 +3295,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:22:51.480792+00:00</t>
+          <t xml:space="preserve">2026-08-25T10:24:21.087549+00:00</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3307,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3319,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,7 +161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -226,12 +226,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,7 +273,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -338,12 +338,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,7 +385,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -450,12 +450,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,57 +609,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,57 +721,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,57 +1057,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1122,17 +1122,17 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1393,110 +1393,222 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3295,7 +3407,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:21.087549+00:00</t>
+          <t xml:space="preserve">2026-08-25T10:25:08.113182+00:00</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3419,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3431,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,7 +161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
+          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -226,12 +226,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
+          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,7 +273,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -338,12 +338,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,7 +385,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -450,12 +450,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,57 +721,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,57 +833,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1169,57 +1169,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1234,17 +1234,17 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1505,110 +1505,222 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3407,7 +3519,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:25:08.113182+00:00</t>
+          <t xml:space="preserve">2026-08-25T10:27:08.764172+00:00</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3531,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3543,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2165,6 +2165,78 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfundpro</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lead_aug26</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shahrivar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T08:56:06.570Z</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3519,7 +3591,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:27:08.764172+00:00</t>
+          <t xml:space="preserve">2026-08-27T08:56:14.190420+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2596,6 +2596,38 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260827-085808-58AE989F</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سایت نجوا</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T08:58:08.597Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3591,7 +3623,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T08:56:14.190420+00:00</t>
+          <t xml:space="preserve">2026-08-27T08:58:17.071784+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2955,6 +2955,38 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-260827-085953-F9E1888A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رفرال</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paid_referral</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T08:59:53.340Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3623,7 +3655,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T08:58:17.071784+00:00</t>
+          <t xml:space="preserve">2026-08-27T09:00:03.188122+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -3599,6 +3599,63 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-BANNER</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فایل لندینگ رو خانم دهقان داره</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T09:09:42.013Z</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3655,7 +3712,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T09:00:03.188122+00:00</t>
+          <t xml:space="preserve">2026-08-27T09:09:49.539599+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,57 +161,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
+          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">سایت نجوا</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">paid_referral</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -226,37 +226,37 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25</t>
+          <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
+          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,7 +273,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
+          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -338,12 +338,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
+          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,7 +385,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -450,12 +450,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,57 +833,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,57 +945,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1281,57 +1281,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1413,24 +1413,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1617,110 +1617,222 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3712,7 +3824,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T09:09:49.539599+00:00</t>
+          <t xml:space="preserve">2026-08-27T09:10:04.394660+00:00</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3836,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3848,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2387,6 +2387,16 @@
           <t xml:space="preserve">createdAt</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">deletedAt</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">deletedBy</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2419,6 +2429,16 @@
           <t xml:space="preserve">2026-08-19T00:00:00Z</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2451,6 +2471,16 @@
           <t xml:space="preserve">2026-08-19T00:00:00Z</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2470,7 +2500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t xml:space="preserve">deleted</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2481,6 +2511,16 @@
       <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T11:51:54.272Z</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
     </row>
@@ -2515,6 +2555,16 @@
           <t xml:space="preserve">2026-08-19T00:00:00Z</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2547,6 +2597,16 @@
           <t xml:space="preserve">2026-08-19T00:00:00Z</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2579,6 +2639,16 @@
           <t xml:space="preserve">2026-08-19T00:00:00Z</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2611,6 +2681,16 @@
           <t xml:space="preserve">2026-08-19T00:00:00Z</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2643,6 +2723,16 @@
           <t xml:space="preserve">2026-08-25T04:07:36.116Z</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2675,6 +2765,16 @@
           <t xml:space="preserve">2026-08-25T08:47:45.138Z</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2707,6 +2807,16 @@
           <t xml:space="preserve">2026-08-25T10:15:13.819Z</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2737,6 +2847,16 @@
       <c r="F12" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-27T08:58:08.597Z</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -3824,7 +3944,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T09:10:04.394660+00:00</t>
+          <t xml:space="preserve">2026-08-27T11:52:03.272923+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2626,7 +2626,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t xml:space="preserve">deleted</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-08-27T11:52:05.390Z</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t xml:space="preserve">deleted</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-08-27T11:52:10.703Z</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T11:52:03.272923+00:00</t>
+          <t xml:space="preserve">2026-08-27T11:52:15.231493+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2752,7 +2752,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t xml:space="preserve">deleted</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-08-27T11:52:20.030Z</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t xml:space="preserve">deleted</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-08-27T11:52:26.277Z</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t xml:space="preserve">deleted</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-08-27T11:52:33.905Z</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T11:52:15.231493+00:00</t>
+          <t xml:space="preserve">2026-08-27T11:52:35.538388+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2860,6 +2860,384 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260827-115240-DAB37F5B</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بله</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bale</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T11:52:40.568Z</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260827-115242-67F8688B</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">روبیکا</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rubika</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T11:52:42.005Z</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260827-115243-B1889E71</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">روبینو</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rubino</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T11:52:43.649Z</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260827-115245-CFDF4A32</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">یوتیوب</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">youtube</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T11:52:45.091Z</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260827-115246-2721543B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایکس (X)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T11:52:46.589Z</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260827-115249-348ED154</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایمیل — Cmercury</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email_cmercury</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T11:52:49.133Z</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260827-115250-C6CF5E94</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیامک — نجوا</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sms_najva</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T11:52:50.647Z</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260827-115252-8DADD5C2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیامک — یکتانت</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sms_yektanet</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T11:52:52.390Z</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260827-115253-07D4CC15</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وب‌سایت رابین‌سود</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T11:52:53.978Z</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3219,6 +3597,166 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-260827-115255-F3CA1EA7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سوشال — رسانه‌های خودمان</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owned_social</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T11:52:55.489Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-260827-115256-5581F2FA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سوشال — رسانه‌های دیگران / پولی</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paid_social</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T11:52:56.964Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-260827-115258-B8005969</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تبلیغات رسمی پلتفرم (مثل Telegram Ads)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">platform_ads</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T11:52:58.557Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-260827-115259-B1756593</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تبلیغات بنری</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">display</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T11:52:59.934Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-260827-115301-AA9591A2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تبلیغات عملکردی — CPR</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cpr</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T11:53:01.370Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3944,7 +4482,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T11:52:35.538388+00:00</t>
+          <t xml:space="preserve">2026-08-27T11:53:04.959987+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -158,6 +158,1686 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سایت نجوا</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رفرال</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paid_referral</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مدیر اصلی</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IranBroker</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iranbroker</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایران بروکر</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">topic</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عصر قلم</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عصر قلم</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عصر قلم</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260819-073228-B8679789</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین شهریور ماه 1405</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referral</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">referral</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مدیر اصلی</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deleted</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -234,7 +1914,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">تلگرام</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -254,7 +1934,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
@@ -266,7 +1946,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instagram</t>
+          <t xml:space="preserve">اینستاگرام</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -286,24 +1966,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRC-IRANBROKER</t>
+          <t xml:space="preserve">SRC-BALE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">بله</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">bale</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -318,24 +1998,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRC-APARAT</t>
+          <t xml:space="preserve">SRC-RUBIKA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aparat</t>
+          <t xml:space="preserve">روبیکا</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">aparat</t>
+          <t xml:space="preserve">rubika</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -350,24 +2030,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRC-GOOGLE</t>
+          <t xml:space="preserve">SRC-RUBINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google</t>
+          <t xml:space="preserve">روبینو</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">google</t>
+          <t xml:space="preserve">rubino</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -382,24 +2062,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRC-YEKTANET</t>
+          <t xml:space="preserve">SRC-YOUTUBE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yektanet</t>
+          <t xml:space="preserve">یوتیوب</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">yektanet</t>
+          <t xml:space="preserve">youtube</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -414,39 +2094,231 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRC-NAJVA</t>
+          <t xml:space="preserve">SRC-APARAT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Najva</t>
+          <t xml:space="preserve">آپارات</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t xml:space="preserve">aparat</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-X</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایکس (X)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-GOOGLE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">گوگل</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">google</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-EMAIL-MERCURY</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایمیل — Mercury</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercury</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-SMS-NAJVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیامک — نجوا</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t xml:space="preserve">najva</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">active</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">system</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-SMS-YEKTANET</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیامک — یکتانت</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yektanet</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-WEBSITE-ROBINSOOD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وب‌سایت رابین‌سود</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
@@ -492,17 +2364,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED-SMS</t>
+          <t xml:space="preserve">MED-OWNED-SOCIAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SMS</t>
+          <t xml:space="preserve">سوشال — رسانه‌های خودمان</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms</t>
+          <t xml:space="preserve">owned_social</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -517,24 +2389,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED-EMAIL</t>
+          <t xml:space="preserve">MED-PAID-SOCIAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Email</t>
+          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">email</t>
+          <t xml:space="preserve">paid_social</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -549,24 +2421,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED-NATIVE-PAID</t>
+          <t xml:space="preserve">MED-PLATFORM-ADS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Native Paid</t>
+          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">native_paid</t>
+          <t xml:space="preserve">platform_ads</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -581,24 +2453,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED-REFERRAL</t>
+          <t xml:space="preserve">MED-DISPLAY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referral</t>
+          <t xml:space="preserve">تبلیغات بنری</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">referral</t>
+          <t xml:space="preserve">display</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -613,24 +2485,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED-VIDEO</t>
+          <t xml:space="preserve">MED-CPC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Video</t>
+          <t xml:space="preserve">هزینه به‌ازای کلیک (CPC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">video</t>
+          <t xml:space="preserve">cpc</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -645,7 +2517,103 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-REFERRAL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رفرال</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">referral</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-EMAIL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایمیل</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-SMS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیامک</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sms</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
@@ -997,7 +2965,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T06:39:09.362925+00:00</t>
+          <t xml:space="preserve">2026-08-27T12:08:19.558088+00:00</t>
         </is>
       </c>
     </row>
@@ -1009,7 +2977,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
     </row>
@@ -1021,7 +2989,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
     </row>
@@ -1045,7 +3013,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -158,6 +158,1686 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سایت نجوا</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رفرال</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paid_referral</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مدیر اصلی</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IranBroker</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iranbroker</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایران بروکر</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">topic</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عصر قلم</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عصر قلم</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عصر قلم</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260819-073228-B8679789</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین شهریور ماه 1405</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referral</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">referral</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مدیر اصلی</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deleted</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -234,7 +1914,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">تلگرام</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -254,7 +1934,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
@@ -266,7 +1946,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instagram</t>
+          <t xml:space="preserve">اینستاگرام</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -286,24 +1966,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRC-IRANBROKER</t>
+          <t xml:space="preserve">SRC-BALE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">بله</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">bale</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -318,24 +1998,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRC-APARAT</t>
+          <t xml:space="preserve">SRC-RUBIKA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aparat</t>
+          <t xml:space="preserve">روبیکا</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">aparat</t>
+          <t xml:space="preserve">rubika</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -350,24 +2030,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRC-GOOGLE</t>
+          <t xml:space="preserve">SRC-RUBINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google</t>
+          <t xml:space="preserve">روبینو</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">google</t>
+          <t xml:space="preserve">rubino</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -382,24 +2062,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRC-YEKTANET</t>
+          <t xml:space="preserve">SRC-YOUTUBE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yektanet</t>
+          <t xml:space="preserve">یوتیوب</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">yektanet</t>
+          <t xml:space="preserve">youtube</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -414,24 +2094,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRC-NAJVA</t>
+          <t xml:space="preserve">SRC-APARAT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Najva</t>
+          <t xml:space="preserve">آپارات</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">najva</t>
+          <t xml:space="preserve">aparat</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -446,7 +2126,199 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-X</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایکس (X)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-GOOGLE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">گوگل</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">google</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-EMAIL-MERCURY</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایمیل — Mercury</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email_mercury</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-SMS-NAJVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیامک — نجوا</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sms_najva</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-SMS-YEKTANET</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیامک — یکتانت</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sms_yektanet</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-WEBSITE-ROBINSOOD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وب‌سایت رابین‌سود</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
@@ -492,17 +2364,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED-SMS</t>
+          <t xml:space="preserve">MED-OWNED-SOCIAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SMS</t>
+          <t xml:space="preserve">سوشال — رسانه‌های خودمان</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms</t>
+          <t xml:space="preserve">owned_social</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -517,24 +2389,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED-EMAIL</t>
+          <t xml:space="preserve">MED-PAID-SOCIAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Email</t>
+          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">email</t>
+          <t xml:space="preserve">paid_social</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -549,24 +2421,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED-NATIVE-PAID</t>
+          <t xml:space="preserve">MED-PLATFORM-ADS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Native Paid</t>
+          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">native_paid</t>
+          <t xml:space="preserve">platform_ads</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -581,24 +2453,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED-REFERRAL</t>
+          <t xml:space="preserve">MED-DISPLAY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referral</t>
+          <t xml:space="preserve">تبلیغات بنری</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">referral</t>
+          <t xml:space="preserve">display</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -613,24 +2485,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED-VIDEO</t>
+          <t xml:space="preserve">MED-CPC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Video</t>
+          <t xml:space="preserve">هزینه به‌ازای کلیک (CPC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">video</t>
+          <t xml:space="preserve">cpc</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -645,7 +2517,103 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-REFERRAL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رفرال</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">referral</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-EMAIL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایمیل</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-SMS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیامک</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sms</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
@@ -997,7 +2965,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T06:39:09.362925+00:00</t>
+          <t xml:space="preserve">2026-08-27T12:30:30.163389+00:00</t>
         </is>
       </c>
     </row>
@@ -1009,7 +2977,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
     </row>
@@ -1021,7 +2989,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
     </row>
@@ -1045,7 +3013,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2880,6 +2880,38 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-260827-123300-59EF956E</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landing</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landing</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T12:33:00.123Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2965,7 +2997,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:30:30.163389+00:00</t>
+          <t xml:space="preserve">2026-08-27T12:33:09.092651+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2937,7 +2937,79 @@
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">contentTypeId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">version</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">createdBy</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">createdAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260827-123456-4C7E9E25</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landing_cr_260827_123456_4c7e9e25_v1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-260827-123300-59EF956E</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فایل لندینگ رو خانم دهقان داره</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T12:34:56.455Z</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3069,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:33:09.092651+00:00</t>
+          <t xml:space="preserve">2026-08-27T12:35:08.160708+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -1863,7 +1863,109 @@
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">product</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">objective</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">period</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">year</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">startDate</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">endDate</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">createdBy</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">createdAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260827-124023-89A94BB0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfundpro</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lead_aug26</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shahrivar</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T12:40:23.993Z</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3171,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:35:08.160708+00:00</t>
+          <t xml:space="preserve">2026-08-27T12:40:34.765884+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -158,6 +158,1686 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سایت نجوا</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رفرال</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paid_referral</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مدیر اصلی</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVOSH</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chavosh</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IranBroker</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iranbroker</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایران بروکر</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">topic</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عصر قلم</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عصر قلم</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عصر قلم</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260819-073228-B8679789</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین شهریور ماه 1405</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referral</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">referral</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مدیر اصلی</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deleted</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -234,7 +1914,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">تلگرام</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -254,7 +1934,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
@@ -266,7 +1946,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instagram</t>
+          <t xml:space="preserve">اینستاگرام</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -286,24 +1966,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRC-IRANBROKER</t>
+          <t xml:space="preserve">SRC-BALE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">بله</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">bale</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -318,24 +1998,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRC-APARAT</t>
+          <t xml:space="preserve">SRC-RUBIKA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aparat</t>
+          <t xml:space="preserve">روبیکا</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">aparat</t>
+          <t xml:space="preserve">rubika</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -350,24 +2030,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRC-GOOGLE</t>
+          <t xml:space="preserve">SRC-RUBINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google</t>
+          <t xml:space="preserve">روبینو</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">google</t>
+          <t xml:space="preserve">rubino</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -382,24 +2062,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRC-YEKTANET</t>
+          <t xml:space="preserve">SRC-YOUTUBE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yektanet</t>
+          <t xml:space="preserve">یوتیوب</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">yektanet</t>
+          <t xml:space="preserve">youtube</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -414,24 +2094,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRC-NAJVA</t>
+          <t xml:space="preserve">SRC-APARAT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Najva</t>
+          <t xml:space="preserve">آپارات</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">najva</t>
+          <t xml:space="preserve">aparat</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -446,7 +2126,199 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-X</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایکس (X)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-GOOGLE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">گوگل</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">google</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-EMAIL-MERCURY</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایمیل — Mercury</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email_mercury</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-SMS-NAJVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیامک — نجوا</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sms_najva</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-SMS-YEKTANET</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیامک — یکتانت</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sms_yektanet</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-WEBSITE-ROBINSOOD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وب‌سایت رابین‌سود</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
@@ -492,17 +2364,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED-SMS</t>
+          <t xml:space="preserve">MED-OWNED-SOCIAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SMS</t>
+          <t xml:space="preserve">سوشال — رسانه‌های خودمان</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms</t>
+          <t xml:space="preserve">owned_social</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -517,24 +2389,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED-EMAIL</t>
+          <t xml:space="preserve">MED-PAID-SOCIAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Email</t>
+          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">email</t>
+          <t xml:space="preserve">paid_social</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -549,24 +2421,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED-NATIVE-PAID</t>
+          <t xml:space="preserve">MED-PLATFORM-ADS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Native Paid</t>
+          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">native_paid</t>
+          <t xml:space="preserve">platform_ads</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -581,24 +2453,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED-REFERRAL</t>
+          <t xml:space="preserve">MED-DISPLAY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referral</t>
+          <t xml:space="preserve">تبلیغات بنری</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">referral</t>
+          <t xml:space="preserve">display</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -613,24 +2485,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MED-VIDEO</t>
+          <t xml:space="preserve">MED-CPC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Video</t>
+          <t xml:space="preserve">هزینه به‌ازای کلیک (CPC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">video</t>
+          <t xml:space="preserve">cpc</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -645,7 +2517,103 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T00:00:00Z</t>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-REFERRAL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رفرال</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">referral</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-EMAIL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایمیل</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MED-SMS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیامک</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sms</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T00:00:00Z</t>
         </is>
       </c>
     </row>
@@ -997,7 +2965,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19T06:39:09.362925+00:00</t>
+          <t xml:space="preserve">2026-08-27T12:46:03.434977+00:00</t>
         </is>
       </c>
     </row>
@@ -1009,7 +2977,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
     </row>
@@ -1021,7 +2989,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
     </row>
@@ -1045,7 +3013,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2880,6 +2880,38 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-260827-124724-E0E58232</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landing</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landing</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T12:47:24.324Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2965,7 +2997,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:46:03.434977+00:00</t>
+          <t xml:space="preserve">2026-08-27T12:47:33.346519+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2937,7 +2937,79 @@
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">contentTypeId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">version</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">createdBy</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">createdAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260827-124734-652CA150</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-260827-124724-E0E58232</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فایل لندینگ رو خانم دهقان داره</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T12:47:34.762Z</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3069,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:47:33.346519+00:00</t>
+          <t xml:space="preserve">2026-08-27T12:47:42.321659+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2322,6 +2322,38 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260827-125023-1FAEFBFB</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سایت نجوا</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T12:50:23.679Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3069,7 +3101,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:47:42.321659+00:00</t>
+          <t xml:space="preserve">2026-08-27T12:50:33.690338+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -1863,7 +1863,109 @@
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">product</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">objective</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">period</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">year</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">startDate</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">endDate</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">createdBy</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">createdAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfundpro</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lead_aug26</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shahrivar</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27T12:50:38.412Z</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3203,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:50:33.690338+00:00</t>
+          <t xml:space="preserve">2026-08-27T12:50:46.854441+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,12 +161,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
+          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
+          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -191,17 +191,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">رفرال</t>
+          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_referral</t>
+          <t xml:space="preserve">paid_social</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
+          <t xml:space="preserve">CR-260827-124734-652CA150</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -211,7 +211,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
+          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,57 +273,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
+          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">سایت نجوا</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">paid_referral</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -338,37 +338,37 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25</t>
+          <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
+          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,7 +385,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
+          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -450,12 +450,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
+          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,57 +945,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,57 +1057,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1393,57 +1393,57 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1458,17 +1458,17 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1525,24 +1525,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1729,110 +1729,222 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="P17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3203,7 +3315,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:50:46.854441+00:00</t>
+          <t xml:space="preserve">2026-08-27T12:52:03.624874+00:00</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3327,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3339,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2081,6 +2081,68 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfund_pro</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">najva</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shahrivar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-02</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-31T19:17:08.742Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3315,7 +3377,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:52:03.624874+00:00</t>
+          <t xml:space="preserve">2026-08-31T19:17:20.153533+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -3321,6 +3321,53 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-260827-124724-E0E58232</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-31T19:19:51.907Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3377,7 +3424,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31T19:17:20.153533+00:00</t>
+          <t xml:space="preserve">2026-08-31T19:20:02.261066+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,57 +161,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
+          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
+          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
+          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
+          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا</t>
+          <t xml:space="preserve">پیامک — نجوا</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_app_cmercury_com</t>
+          <t xml:space="preserve">sms_najva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
+          <t xml:space="preserve">پیامک</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_social</t>
+          <t xml:space="preserve">sms</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-124734-652CA150</t>
+          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -231,32 +231,32 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
+          <t xml:space="preserve">NAJVA _ YEKTANET</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیر اصلی</t>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t xml:space="preserve">owner</t>
+          <t xml:space="preserve">marketing</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
+          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,12 +273,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
+          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
+          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -303,17 +303,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">رفرال</t>
+          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_referral</t>
+          <t xml:space="preserve">paid_social</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
+          <t xml:space="preserve">CR-260827-124734-652CA150</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -323,7 +323,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -343,7 +343,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
+          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,57 +385,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
+          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">سایت نجوا</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">paid_referral</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -450,37 +450,37 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25</t>
+          <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
+          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
+          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
+          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,57 +1057,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1169,57 +1169,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1505,57 +1505,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1570,17 +1570,17 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1637,24 +1637,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1841,110 +1841,222 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
+      <c r="P18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3424,7 +3536,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31T19:20:02.261066+00:00</t>
+          <t xml:space="preserve">2026-08-31T19:21:26.839621+00:00</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3548,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3560,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2255,6 +2255,68 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260831-200113-3FFD5992</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین گزارش خبری عصر قلم</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shahrivar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-30</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-05-30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-31T20:01:13.184Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3536,7 +3598,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31T19:21:26.839621+00:00</t>
+          <t xml:space="preserve">2026-08-31T20:01:22.229770+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2804,6 +2804,38 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260901-061218-8C0A3122</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سایت نجوا پیامک</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">site-https_www_najva_com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-01T06:12:18.813Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3598,7 +3630,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31T20:01:22.229770+00:00</t>
+          <t xml:space="preserve">2026-09-01T06:12:29.305070+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,7 +161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
+          <t xml:space="preserve">UTM-260901-061312-E59AAE83</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -181,12 +181,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیامک — نجوا</t>
+          <t xml:space="preserve">سایت نجوا پیامک</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms_najva</t>
+          <t xml:space="preserve">site-https_www_najva_com</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -226,37 +226,37 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=site-https_www_najva_com&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAJVA _ YEKTANET</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
+          <t xml:space="preserve">2026-09-01T06:13:12.719Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,57 +273,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
+          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
+          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
+          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
+          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا</t>
+          <t xml:space="preserve">پیامک — نجوا</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_app_cmercury_com</t>
+          <t xml:space="preserve">sms_najva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
+          <t xml:space="preserve">پیامک</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_social</t>
+          <t xml:space="preserve">sms</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-124734-652CA150</t>
+          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -343,32 +343,32 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
+          <t xml:space="preserve">NAJVA _ YEKTANET</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیر اصلی</t>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t xml:space="preserve">owner</t>
+          <t xml:space="preserve">marketing</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
+          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,12 +385,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
+          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
+          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -415,17 +415,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">رفرال</t>
+          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_referral</t>
+          <t xml:space="preserve">paid_social</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
+          <t xml:space="preserve">CR-260827-124734-652CA150</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -435,7 +435,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -455,7 +455,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
+          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,57 +497,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
+          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">سایت نجوا</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">paid_referral</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -562,37 +562,37 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25</t>
+          <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
+          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
+          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
+          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1169,57 +1169,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1281,57 +1281,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1617,57 +1617,57 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1682,17 +1682,17 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1749,24 +1749,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1953,110 +1953,222 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
+      <c r="P19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3630,7 +3742,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T06:12:29.305070+00:00</t>
+          <t xml:space="preserve">2026-09-01T06:13:20.643665+00:00</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3754,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2429,6 +2429,68 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260901-085307-6BB54908</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین تلگرام ادز</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfundpro_lead_generation_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfundpro</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lead_generation</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shahrivar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-01T08:53:07.985Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3742,7 +3804,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T06:13:20.643665+00:00</t>
+          <t xml:space="preserve">2026-09-01T08:53:17.321809+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -3748,6 +3748,53 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260901-085439-FE513724</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لندینگ اصلی رابین سود نسخه 1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landing_cr_260901_085439_fe513724_v1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-260827-124724-E0E58232</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-01T08:54:39.488Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3804,7 +3851,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T08:53:17.321809+00:00</t>
+          <t xml:space="preserve">2026-09-01T08:54:50.631515+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,57 +161,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-061312-E59AAE83</t>
+          <t xml:space="preserve">UTM-260901-085808-9F62A258</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
+          <t xml:space="preserve">CMP-260901-085307-6BB54908</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
+          <t xml:space="preserve">کمپین تلگرام ادز</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_generation_shahrivar_1405</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا پیامک</t>
+          <t xml:space="preserve">تلگرام</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_www_najva_com</t>
+          <t xml:space="preserve">telegram</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیامک</t>
+          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms</t>
+          <t xml:space="preserve">platform_ads</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
+          <t xml:space="preserve">CR-260901-085439-FE513724</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ اصلی رابین سود نسخه 1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">landing_cr_260901_085439_fe513724_v1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -226,12 +226,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://landing.robinsood.com/</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=site-https_www_najva_com&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">https://landing.robinsood.com/?utm_source=telegram&amp;utm_medium=platform_ads&amp;utm_campaign=fullfundpro_lead_generation_shahrivar_1405&amp;utm_content=landing_cr_260901_085439_fe513724_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T06:13:12.719Z</t>
+          <t xml:space="preserve">2026-09-01T08:58:08.438Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,7 +273,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
+          <t xml:space="preserve">UTM-260901-061312-E59AAE83</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -293,12 +293,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیامک — نجوا</t>
+          <t xml:space="preserve">سایت نجوا پیامک</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms_najva</t>
+          <t xml:space="preserve">site-https_www_najva_com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -338,37 +338,37 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=site-https_www_najva_com&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAJVA _ YEKTANET</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
+          <t xml:space="preserve">2026-09-01T06:13:12.719Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,57 +385,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
+          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
+          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
+          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
+          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا</t>
+          <t xml:space="preserve">پیامک — نجوا</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_app_cmercury_com</t>
+          <t xml:space="preserve">sms_najva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
+          <t xml:space="preserve">پیامک</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_social</t>
+          <t xml:space="preserve">sms</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-124734-652CA150</t>
+          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -455,32 +455,32 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
+          <t xml:space="preserve">NAJVA _ YEKTANET</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیر اصلی</t>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve">owner</t>
+          <t xml:space="preserve">marketing</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
+          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,12 +497,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
+          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
+          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -527,17 +527,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">رفرال</t>
+          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_referral</t>
+          <t xml:space="preserve">paid_social</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
+          <t xml:space="preserve">CR-260827-124734-652CA150</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
+          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,57 +609,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
+          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">سایت نجوا</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">paid_referral</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -674,37 +674,37 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25</t>
+          <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
+          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
+          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
+          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1281,57 +1281,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1393,57 +1393,57 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1729,57 +1729,57 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1794,17 +1794,17 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1953,7 +1953,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2065,110 +2065,222 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
+      <c r="P20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3851,7 +3963,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T08:54:50.631515+00:00</t>
+          <t xml:space="preserve">2026-09-01T08:58:16.957008+00:00</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3975,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
     </row>
@@ -3875,7 +3987,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -3122,6 +3122,38 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260901-110419-8B76953F</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عصر قلم</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https_asreqalam_com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-01T11:04:19.167Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3963,7 +3995,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T08:58:16.957008+00:00</t>
+          <t xml:space="preserve">2026-09-01T11:04:28.346051+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -3939,6 +3939,53 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260901-110923-EE09CA3B</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inner link</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260901_110923_ee09ca3b_v1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-TEXT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-01T11:09:23.059Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3995,7 +4042,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:04:28.346051+00:00</t>
+          <t xml:space="preserve">2026-09-01T11:09:32.122910+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,57 +161,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-085808-9F62A258</t>
+          <t xml:space="preserve">UTM-260901-111033-45E08A6B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260901-085307-6BB54908</t>
+          <t xml:space="preserve">CMP-260831-200113-3FFD5992</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین تلگرام ادز</t>
+          <t xml:space="preserve">کمپین گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfundpro_lead_generation_shahrivar_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">تلگرام</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">https_asreqalam_com</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">platform_ads</t>
+          <t xml:space="preserve">referral</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260901-085439-FE513724</t>
+          <t xml:space="preserve">CR-260901-110923-EE09CA3B</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ اصلی رابین سود نسخه 1</t>
+          <t xml:space="preserve">inner link</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260901_085439_fe513724_v1</t>
+          <t xml:space="preserve">text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -226,17 +226,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://landing.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://landing.robinsood.com/?utm_source=telegram&amp;utm_medium=platform_ads&amp;utm_campaign=fullfundpro_lead_generation_shahrivar_1405&amp;utm_content=landing_cr_260901_085439_fe513724_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">5 عدد گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -246,17 +246,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیر اصلی</t>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t xml:space="preserve">owner</t>
+          <t xml:space="preserve">marketing</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T08:58:08.438Z</t>
+          <t xml:space="preserve">2026-09-01T11:10:33.037Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,57 +273,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-061312-E59AAE83</t>
+          <t xml:space="preserve">UTM-260901-085808-9F62A258</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
+          <t xml:space="preserve">CMP-260901-085307-6BB54908</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
+          <t xml:space="preserve">کمپین تلگرام ادز</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_generation_shahrivar_1405</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا پیامک</t>
+          <t xml:space="preserve">تلگرام</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_www_najva_com</t>
+          <t xml:space="preserve">telegram</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیامک</t>
+          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms</t>
+          <t xml:space="preserve">platform_ads</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
+          <t xml:space="preserve">CR-260901-085439-FE513724</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ اصلی رابین سود نسخه 1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">landing_cr_260901_085439_fe513724_v1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -338,12 +338,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://landing.robinsood.com/</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=site-https_www_najva_com&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">https://landing.robinsood.com/?utm_source=telegram&amp;utm_medium=platform_ads&amp;utm_campaign=fullfundpro_lead_generation_shahrivar_1405&amp;utm_content=landing_cr_260901_085439_fe513724_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T06:13:12.719Z</t>
+          <t xml:space="preserve">2026-09-01T08:58:08.438Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,7 +385,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
+          <t xml:space="preserve">UTM-260901-061312-E59AAE83</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -405,12 +405,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیامک — نجوا</t>
+          <t xml:space="preserve">سایت نجوا پیامک</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms_najva</t>
+          <t xml:space="preserve">site-https_www_najva_com</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -450,37 +450,37 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=site-https_www_najva_com&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAJVA _ YEKTANET</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
+          <t xml:space="preserve">2026-09-01T06:13:12.719Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,57 +497,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
+          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
+          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
+          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
+          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا</t>
+          <t xml:space="preserve">پیامک — نجوا</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_app_cmercury_com</t>
+          <t xml:space="preserve">sms_najva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
+          <t xml:space="preserve">پیامک</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_social</t>
+          <t xml:space="preserve">sms</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-124734-652CA150</t>
+          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -567,32 +567,32 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
+          <t xml:space="preserve">NAJVA _ YEKTANET</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیر اصلی</t>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">owner</t>
+          <t xml:space="preserve">marketing</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
+          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,12 +609,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
+          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
+          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -639,17 +639,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رفرال</t>
+          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_referral</t>
+          <t xml:space="preserve">paid_social</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
+          <t xml:space="preserve">CR-260827-124734-652CA150</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
+          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,57 +721,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
+          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">سایت نجوا</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">paid_referral</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -786,37 +786,37 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25</t>
+          <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
+          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
+          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
+          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1393,57 +1393,57 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1505,57 +1505,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1841,57 +1841,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1906,17 +1906,17 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1953,7 +1953,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1973,24 +1973,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2065,7 +2065,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2177,110 +2177,222 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
+      <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4042,7 +4154,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:09:32.122910+00:00</t>
+          <t xml:space="preserve">2026-09-01T11:10:41.659456+00:00</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4166,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4178,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,7 +161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-111033-45E08A6B</t>
+          <t xml:space="preserve">UTM-260901-111516-E7335995</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -226,12 +226,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:10:33.037Z</t>
+          <t xml:space="preserve">2026-09-01T11:15:16.634Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,57 +273,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-085808-9F62A258</t>
+          <t xml:space="preserve">UTM-260901-111033-45E08A6B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260901-085307-6BB54908</t>
+          <t xml:space="preserve">CMP-260831-200113-3FFD5992</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین تلگرام ادز</t>
+          <t xml:space="preserve">کمپین گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfundpro_lead_generation_shahrivar_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">تلگرام</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">https_asreqalam_com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">platform_ads</t>
+          <t xml:space="preserve">referral</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260901-085439-FE513724</t>
+          <t xml:space="preserve">CR-260901-110923-EE09CA3B</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ اصلی رابین سود نسخه 1</t>
+          <t xml:space="preserve">inner link</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260901_085439_fe513724_v1</t>
+          <t xml:space="preserve">text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -338,17 +338,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://landing.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://landing.robinsood.com/?utm_source=telegram&amp;utm_medium=platform_ads&amp;utm_campaign=fullfundpro_lead_generation_shahrivar_1405&amp;utm_content=landing_cr_260901_085439_fe513724_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">5 عدد گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -358,17 +358,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیر اصلی</t>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t xml:space="preserve">owner</t>
+          <t xml:space="preserve">marketing</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T08:58:08.438Z</t>
+          <t xml:space="preserve">2026-09-01T11:10:33.037Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,57 +385,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-061312-E59AAE83</t>
+          <t xml:space="preserve">UTM-260901-085808-9F62A258</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
+          <t xml:space="preserve">CMP-260901-085307-6BB54908</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
+          <t xml:space="preserve">کمپین تلگرام ادز</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_generation_shahrivar_1405</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا پیامک</t>
+          <t xml:space="preserve">تلگرام</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_www_najva_com</t>
+          <t xml:space="preserve">telegram</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیامک</t>
+          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms</t>
+          <t xml:space="preserve">platform_ads</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
+          <t xml:space="preserve">CR-260901-085439-FE513724</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ اصلی رابین سود نسخه 1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">landing_cr_260901_085439_fe513724_v1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -450,12 +450,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://landing.robinsood.com/</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=site-https_www_najva_com&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">https://landing.robinsood.com/?utm_source=telegram&amp;utm_medium=platform_ads&amp;utm_campaign=fullfundpro_lead_generation_shahrivar_1405&amp;utm_content=landing_cr_260901_085439_fe513724_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T06:13:12.719Z</t>
+          <t xml:space="preserve">2026-09-01T08:58:08.438Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
+          <t xml:space="preserve">UTM-260901-061312-E59AAE83</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -517,12 +517,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیامک — نجوا</t>
+          <t xml:space="preserve">سایت نجوا پیامک</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms_najva</t>
+          <t xml:space="preserve">site-https_www_najva_com</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -562,37 +562,37 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=site-https_www_najva_com&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAJVA _ YEKTANET</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
+          <t xml:space="preserve">2026-09-01T06:13:12.719Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,57 +609,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
+          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
+          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
+          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
+          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا</t>
+          <t xml:space="preserve">پیامک — نجوا</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_app_cmercury_com</t>
+          <t xml:space="preserve">sms_najva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
+          <t xml:space="preserve">پیامک</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_social</t>
+          <t xml:space="preserve">sms</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-124734-652CA150</t>
+          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -679,32 +679,32 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
+          <t xml:space="preserve">NAJVA _ YEKTANET</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیر اصلی</t>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">owner</t>
+          <t xml:space="preserve">marketing</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
+          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,12 +721,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
+          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
+          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">رفرال</t>
+          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_referral</t>
+          <t xml:space="preserve">paid_social</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
+          <t xml:space="preserve">CR-260827-124734-652CA150</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
+          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,57 +833,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
+          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">سایت نجوا</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">paid_referral</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -898,37 +898,37 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25</t>
+          <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
+          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
+          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
+          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1505,57 +1505,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1617,57 +1617,57 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1953,57 +1953,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2018,17 +2018,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2065,7 +2065,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2085,24 +2085,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2177,7 +2177,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2289,110 +2289,222 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="P22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4154,7 +4266,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:10:41.659456+00:00</t>
+          <t xml:space="preserve">2026-09-01T11:15:27.757150+00:00</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4278,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4290,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,7 +161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-111516-E7335995</t>
+          <t xml:space="preserve">UTM-260901-111838-F1589F42</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -226,12 +226,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:15:16.634Z</t>
+          <t xml:space="preserve">2026-09-01T11:18:38.884Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,7 +273,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-111033-45E08A6B</t>
+          <t xml:space="preserve">UTM-260901-111516-E7335995</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -338,12 +338,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:10:33.037Z</t>
+          <t xml:space="preserve">2026-09-01T11:15:16.634Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,57 +385,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-085808-9F62A258</t>
+          <t xml:space="preserve">UTM-260901-111033-45E08A6B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260901-085307-6BB54908</t>
+          <t xml:space="preserve">CMP-260831-200113-3FFD5992</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین تلگرام ادز</t>
+          <t xml:space="preserve">کمپین گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfundpro_lead_generation_shahrivar_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">تلگرام</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">https_asreqalam_com</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">platform_ads</t>
+          <t xml:space="preserve">referral</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260901-085439-FE513724</t>
+          <t xml:space="preserve">CR-260901-110923-EE09CA3B</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ اصلی رابین سود نسخه 1</t>
+          <t xml:space="preserve">inner link</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260901_085439_fe513724_v1</t>
+          <t xml:space="preserve">text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -450,17 +450,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://landing.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://landing.robinsood.com/?utm_source=telegram&amp;utm_medium=platform_ads&amp;utm_campaign=fullfundpro_lead_generation_shahrivar_1405&amp;utm_content=landing_cr_260901_085439_fe513724_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">5 عدد گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -470,17 +470,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیر اصلی</t>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve">owner</t>
+          <t xml:space="preserve">marketing</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T08:58:08.438Z</t>
+          <t xml:space="preserve">2026-09-01T11:10:33.037Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,57 +497,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-061312-E59AAE83</t>
+          <t xml:space="preserve">UTM-260901-085808-9F62A258</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
+          <t xml:space="preserve">CMP-260901-085307-6BB54908</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
+          <t xml:space="preserve">کمپین تلگرام ادز</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_generation_shahrivar_1405</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا پیامک</t>
+          <t xml:space="preserve">تلگرام</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_www_najva_com</t>
+          <t xml:space="preserve">telegram</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیامک</t>
+          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms</t>
+          <t xml:space="preserve">platform_ads</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
+          <t xml:space="preserve">CR-260901-085439-FE513724</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ اصلی رابین سود نسخه 1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">landing_cr_260901_085439_fe513724_v1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://landing.robinsood.com/</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=site-https_www_najva_com&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">https://landing.robinsood.com/?utm_source=telegram&amp;utm_medium=platform_ads&amp;utm_campaign=fullfundpro_lead_generation_shahrivar_1405&amp;utm_content=landing_cr_260901_085439_fe513724_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T06:13:12.719Z</t>
+          <t xml:space="preserve">2026-09-01T08:58:08.438Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
+          <t xml:space="preserve">UTM-260901-061312-E59AAE83</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -629,12 +629,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیامک — نجوا</t>
+          <t xml:space="preserve">سایت نجوا پیامک</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms_najva</t>
+          <t xml:space="preserve">site-https_www_najva_com</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -674,37 +674,37 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=site-https_www_najva_com&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAJVA _ YEKTANET</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
+          <t xml:space="preserve">2026-09-01T06:13:12.719Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,57 +721,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
+          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
+          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
+          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
+          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا</t>
+          <t xml:space="preserve">پیامک — نجوا</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_app_cmercury_com</t>
+          <t xml:space="preserve">sms_najva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
+          <t xml:space="preserve">پیامک</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_social</t>
+          <t xml:space="preserve">sms</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-124734-652CA150</t>
+          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -791,32 +791,32 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
+          <t xml:space="preserve">NAJVA _ YEKTANET</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیر اصلی</t>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve">owner</t>
+          <t xml:space="preserve">marketing</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
+          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,12 +833,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
+          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
+          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -863,17 +863,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">رفرال</t>
+          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_referral</t>
+          <t xml:space="preserve">paid_social</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
+          <t xml:space="preserve">CR-260827-124734-652CA150</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
+          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,57 +945,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
+          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">سایت نجوا</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">paid_referral</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1010,37 +1010,37 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25</t>
+          <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
+          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
+          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
+          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1617,57 +1617,57 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1729,57 +1729,57 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1953,7 +1953,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2065,57 +2065,57 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2130,17 +2130,17 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2177,7 +2177,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,24 +2197,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2289,7 +2289,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2401,110 +2401,222 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
+      <c r="P23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4266,7 +4378,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:15:27.757150+00:00</t>
+          <t xml:space="preserve">2026-09-01T11:18:47.483083+00:00</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4390,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4402,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -2939,6 +2939,68 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260908-111715-8FB3E495</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو شهریورماه</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfund_pro_iran_broker_topic_shahrivar_1405</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fullfund_pro</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iran_broker_topic</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shahrivar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-12-16</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08T11:17:15.518Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -4378,7 +4440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:18:47.483083+00:00</t>
+          <t xml:space="preserve">2026-09-08T11:17:24.974637+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -3552,6 +3552,38 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC-260908-111906-EE7204A0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کامیونیتی ایران بروکر</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https_forum_iranbroker_net</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08T11:19:06.875Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -4440,7 +4472,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:17:24.974637+00:00</t>
+          <t xml:space="preserve">2026-09-08T11:19:16.281627+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -4416,6 +4416,53 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260908-112705-05380120</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260908_112705_05380120_v1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-TEXT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08T11:27:05.740Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -4472,7 +4519,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:19:16.281627+00:00</t>
+          <t xml:space="preserve">2026-09-08T11:27:13.341742+00:00</t>
         </is>
       </c>
     </row>

--- a/exports/utm_history.xlsx
+++ b/exports/utm_history.xlsx
@@ -161,57 +161,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-111838-F1589F42</t>
+          <t xml:space="preserve">UTM-260908-112751-C889CFF2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260831-200113-3FFD5992</t>
+          <t xml:space="preserve">CMP-260908-111715-8FB3E495</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو شهریورماه</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">fullfund_pro_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">کامیونیتی ایران بروکر</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https_asreqalam_com</t>
+          <t xml:space="preserve">https_forum_iranbroker_net</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">رفرال</t>
+          <t xml:space="preserve">تبلیغات بنری</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">referral</t>
+          <t xml:space="preserve">display</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260901-110923-EE09CA3B</t>
+          <t xml:space="preserve">CR-260908-112705-05380120</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">inner link</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">text_cr_260908_112705_05380120_v1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -226,22 +226,22 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=https_forum_iranbroker_net&amp;utm_medium=display&amp;utm_campaign=fullfund_pro_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260908_112705_05380120_v1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 عدد گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کامیونیتی ایران بروکر</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -256,7 +256,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:18:38.884Z</t>
+          <t xml:space="preserve">2026-09-08T11:27:51.066Z</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -273,7 +273,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-111516-E7335995</t>
+          <t xml:space="preserve">UTM-260901-111838-F1589F42</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -338,12 +338,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:15:16.634Z</t>
+          <t xml:space="preserve">2026-09-01T11:18:38.884Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -385,7 +385,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-111033-45E08A6B</t>
+          <t xml:space="preserve">UTM-260901-111516-E7335995</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -450,12 +450,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T11:10:33.037Z</t>
+          <t xml:space="preserve">2026-09-01T11:15:16.634Z</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -497,57 +497,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-085808-9F62A258</t>
+          <t xml:space="preserve">UTM-260901-111033-45E08A6B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260901-085307-6BB54908</t>
+          <t xml:space="preserve">CMP-260831-200113-3FFD5992</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین تلگرام ادز</t>
+          <t xml:space="preserve">کمپین گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfundpro_lead_generation_shahrivar_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">تلگرام</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">https_asreqalam_com</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">platform_ads</t>
+          <t xml:space="preserve">referral</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260901-085439-FE513724</t>
+          <t xml:space="preserve">CR-260901-110923-EE09CA3B</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ اصلی رابین سود نسخه 1</t>
+          <t xml:space="preserve">inner link</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260901_085439_fe513724_v1</t>
+          <t xml:space="preserve">text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -562,17 +562,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://landing.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://landing.robinsood.com/?utm_source=telegram&amp;utm_medium=platform_ads&amp;utm_campaign=fullfundpro_lead_generation_shahrivar_1405&amp;utm_content=landing_cr_260901_085439_fe513724_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=https_asreqalam_com&amp;utm_medium=referral&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260901_110923_ee09ca3b_v1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">5 عدد گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -582,17 +582,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیر اصلی</t>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">owner</t>
+          <t xml:space="preserve">marketing</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T08:58:08.438Z</t>
+          <t xml:space="preserve">2026-09-01T11:10:33.037Z</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -609,57 +609,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260901-061312-E59AAE83</t>
+          <t xml:space="preserve">UTM-260901-085808-9F62A258</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
+          <t xml:space="preserve">CMP-260901-085307-6BB54908</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
+          <t xml:space="preserve">کمپین تلگرام ادز</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_generation_shahrivar_1405</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا پیامک</t>
+          <t xml:space="preserve">تلگرام</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_www_najva_com</t>
+          <t xml:space="preserve">telegram</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیامک</t>
+          <t xml:space="preserve">سوشال رسمی / تبلیغات پلتفرمی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms</t>
+          <t xml:space="preserve">platform_ads</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
+          <t xml:space="preserve">CR-260901-085439-FE513724</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ اصلی رابین سود نسخه 1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">landing_cr_260901_085439_fe513724_v1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://landing.robinsood.com/</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=site-https_www_najva_com&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">https://landing.robinsood.com/?utm_source=telegram&amp;utm_medium=platform_ads&amp;utm_campaign=fullfundpro_lead_generation_shahrivar_1405&amp;utm_content=landing_cr_260901_085439_fe513724_v1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01T06:13:12.719Z</t>
+          <t xml:space="preserve">2026-09-01T08:58:08.438Z</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
+          <t xml:space="preserve">UTM-260901-061312-E59AAE83</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیامک — نجوا</t>
+          <t xml:space="preserve">سایت نجوا پیامک</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms_najva</t>
+          <t xml:space="preserve">site-https_www_najva_com</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -786,37 +786,37 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=site-https_www_najva_com&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAJVA _ YEKTANET</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
+          <t xml:space="preserve">2026-09-01T06:13:12.719Z</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -833,57 +833,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
+          <t xml:space="preserve">UTM-260831-192118-35297D77</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
+          <t xml:space="preserve">CMP-260831-191708-22583F97</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
+          <t xml:space="preserve">کمپین sms  مارکتنیگ افزایش لید فول فاند پرو شهریور</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
+          <t xml:space="preserve">fullfund_pro_najva_shahrivar_1405</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا</t>
+          <t xml:space="preserve">پیامک — نجوا</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">site-https_app_cmercury_com</t>
+          <t xml:space="preserve">sms_najva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
+          <t xml:space="preserve">پیامک</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_social</t>
+          <t xml:space="preserve">sms</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-124734-652CA150</t>
+          <t xml:space="preserve">CR-260831-191951-166E33F1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
+          <t xml:space="preserve">لندینگ آموزشی پیامک نجوا لیدگیری فول فاند پرو</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -903,32 +903,32 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=sms_najva&amp;utm_medium=sms&amp;utm_campaign=fullfund_pro_najva_shahrivar_1405&amp;utm_content=landing_cr_260831_191951_166e33f1_v1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
+          <t xml:space="preserve">NAJVA _ YEKTANET</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیر اصلی</t>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">owner</t>
+          <t xml:space="preserve">marketing</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
+          <t xml:space="preserve">2026-08-31T19:21:18.902Z</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -945,12 +945,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
+          <t xml:space="preserve">UTM-260827-125155-21514E11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
+          <t xml:space="preserve">CMP-260827-125038-911A460E</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -975,17 +975,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">رفرال</t>
+          <t xml:space="preserve">سوشال — رسانه دیگران (تبلیغ پولی)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">paid_referral</t>
+          <t xml:space="preserve">paid_social</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
+          <t xml:space="preserve">CR-260827-124734-652CA150</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_social&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=landing_cr_260827_124734_652ca150_v1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
+          <t xml:space="preserve">2026-08-27T12:51:55.977Z</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1057,57 +1057,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
+          <t xml:space="preserve">UTM-260827-090956-92F01974</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
+          <t xml:space="preserve">CMP-260827-085606-E8BBADD6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
+          <t xml:space="preserve">کمپین ایمیل مارکتینگ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
+          <t xml:space="preserve">fullfundpro_lead_aug26_shahrivar_1405</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">سایت نجوا</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">site-https_app_cmercury_com</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVOSH</t>
+          <t xml:space="preserve">رفرال</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">chavosh</t>
+          <t xml:space="preserve">paid_referral</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
+          <t xml:space="preserve">CR-260827-090942-2D63B607</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
+          <t xml:space="preserve">لندینگ بعد از رونمایی فول فاند پرو</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1122,37 +1122,37 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=site-https_app_cmercury_com&amp;utm_medium=paid_referral&amp;utm_campaign=fullfundpro_lead_aug26_shahrivar_1405&amp;utm_content=banner_cr_260827_090942_2d63b607_v1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">سایت نجوا برای ارسال ایمیل</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25</t>
+          <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t xml:space="preserve">مسئول مارکتینگ</t>
+          <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t xml:space="preserve">marketing</t>
+          <t xml:space="preserve">owner</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
+          <t xml:space="preserve">2026-08-27T09:09:56.556Z</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
+          <t xml:space="preserve">UTM-260825-102659-8E931923</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.aparat.com/robinsood?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
+          <t xml:space="preserve">2026-08-25T10:26:59.420Z</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
+          <t xml:space="preserve">UTM-260825-102459-F0C15863</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:59.548Z</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
+          <t xml:space="preserve">UTM-260825-102412-3F3D14C5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2137/%D9%BE%D9%84%D8%AA%D9%81%D8%B1%D9%85-%D9%85%D8%B9%D8%A7%D9%85%D9%84%D8%A7%D8%AA%DB%8C-%D8%A7%D8%AE%D8%AA%D8%B5%D8%A7%D8%B5%DB%8C-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF%D8%9B-%D8%B2%DB%8C%D8%B1%D8%B3%D8%A7%D8%AE%D8%AA%DB%8C-%D9%BE%D8%A7%DB%8C%D8%AF%D8%A7%D8%B1-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C-%D8%AF%D8%B1-%D8%B9%D8%B5%D8%B1-%D8%A7%DB%8C%D9%86%D8%AA%D8%B1%D9%86%D8%AA-%D9%85%D9%84%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
+          <t xml:space="preserve">2026-08-25T10:24:12.118Z</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
+          <t xml:space="preserve">UTM-260825-102243-CE4C221C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
+          <t xml:space="preserve">https://www.robinsood.com/articledetails/2138/%D9%BE%D9%86%D9%84-%D8%A2%D9%86%D8%A7%D9%84%DB%8C%D8%B2-%D8%B1%D8%A7%D8%A8%DB%8C%D9%86%E2%80%8C%D8%B3%D9%88%D8%AF-%D8%A8%D9%87%E2%80%8C%D8%B1%D9%88%D8%B2-%D8%B4%D8%AF%D8%9B-%D8%A7%D8%A8%D8%B2%D8%A7%D8%B1-%D8%AD%D8%B1%D9%81%D9%87%E2%80%8C%D8%A7%DB%8C-%D8%AA%D8%AD%D9%84%DB%8C%D9%84-%D8%B9%D9%85%D9%84%DA%A9%D8%B1%D8%AF-%D8%A8%D8%B1%D8%A7%DB%8C-%D8%AA%D8%B1%DB%8C%D8%AF%D8%B1%D9%87%D8%A7%DB%8C-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%DB%8C?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
+          <t xml:space="preserve">2026-08-25T10:22:43.898Z</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
+          <t xml:space="preserve">UTM-260825-101921-C284C5C7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1#Tariff</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
+          <t xml:space="preserve">2026-08-25T10:19:21.530Z</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1729,57 +1729,57 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
+          <t xml:space="preserve">UTM-260825-101706-3EB39CD7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
+          <t xml:space="preserve">CMP-260825-101424-53264E8F</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
+          <t xml:space="preserve">چاوش کمپین شهریور ماه</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
+          <t xml:space="preserve">fullfun_pro_chavosh_shahrivar_1405</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">IranBroker</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">iranbroker</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایران بروکر</t>
+          <t xml:space="preserve">CHAVOSH</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">chavosh</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
+          <t xml:space="preserve">CR-260825-101625-18413FD9</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">تاپیک ایران بروکر</t>
+          <t xml:space="preserve">لینک داخلی لندینگ چاوش</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=chavosh&amp;utm_medium=chavosh&amp;utm_campaign=fullfun_pro_chavosh_shahrivar_1405&amp;utm_content=text_cr_260825_101625_18413fd9_v1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
+          <t xml:space="preserve">2026-08-25T10:17:06.437Z</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1841,57 +1841,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
+          <t xml:space="preserve">UTM-260825-091655-E22F4CDC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
+          <t xml:space="preserve">CMP-260825-091540-3723FD1E</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">گزارش خبری عصر قلم</t>
+          <t xml:space="preserve">کمپین جذب فول فاند پرو و افزایش احراز هویت و ثبت نام شهریور</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
+          <t xml:space="preserve">w1_iran_broker_topic_shahrivar_1405</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">عصر قلم</t>
+          <t xml:space="preserve">IranBroker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">iranbroker</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ریپورتاژ</t>
+          <t xml:space="preserve">ایران بروکر</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
+          <t xml:space="preserve">CR-260825-091651-2FF9319F</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
+          <t xml:space="preserve">تاپیک ایران بروکر</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=iranbroker&amp;utm_medium=topic&amp;utm_campaign=w1_iran_broker_topic_shahrivar_1405&amp;utm_content=text_cr_260825_091651_2ff9319f_v1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
+          <t xml:space="preserve">2026-08-25T09:16:55.479Z</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1953,7 +1953,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
+          <t xml:space="preserve">UTM-260825-085025-354A85BE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/faq?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
+          <t xml:space="preserve">2026-08-25T08:50:25.139Z</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2065,7 +2065,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
+          <t xml:space="preserve">UTM-260825-084937-A80CCA60</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/contact?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
+          <t xml:space="preserve">2026-08-25T08:49:37.863Z</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2177,57 +2177,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
+          <t xml:space="preserve">UTM-260825-084841-EAB285FA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+          <t xml:space="preserve">CMP-260825-084630-4096D1CA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+          <t xml:space="preserve">گزارش خبری عصر قلم</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+          <t xml:space="preserve">robinsood_report_shahrivar_1405</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram</t>
+          <t xml:space="preserve">عصر قلم</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">telegram</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">ریپورتاژ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinsood_channel</t>
+          <t xml:space="preserve">report</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+          <t xml:space="preserve">CR-260825-084809-D27D6486</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">پیام متنی کانال</t>
+          <t xml:space="preserve">لینک داخلی ریپورتاژ</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
+          <t xml:space="preserve">https://www.robinsood.com/</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=report&amp;utm_medium=report&amp;utm_campaign=robinsood_report_shahrivar_1405&amp;utm_content=text_cr_260825_084809_d27d6486_v1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram channel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
+          <t xml:space="preserve">2026-08-25T08:48:41.603Z</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2289,7 +2289,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
+          <t xml:space="preserve">UTM-260825-042901-A14298C2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2309,24 +2309,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">telegram</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">robinsood_channel</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinsood_channel</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
+          <t xml:space="preserve">https://www.robinsood.com/account/userlogin?utm_source=telegram&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
+          <t xml:space="preserve">2026-08-25T04:29:01.059Z</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+          <t xml:space="preserve">UTM-260825-041822-C649E3F3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+          <t xml:space="preserve">https://pegah.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+          <t xml:space="preserve">2026-08-25T04:18:22.597Z</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2513,110 +2513,222 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t xml:space="preserve">UTM-260825-040749-6A267E6A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CMP-260825-040435-CA37AC31</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام‌های متنی روزانه</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other_challenges_challenges_cost_ever_1405</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinsood_channel</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-260825-040046-DDF1BDDC</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پیام متنی کانال</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text_cr_260825_040046_ddf1bddc_v1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/#Tariff</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.robinsood.com/?utm_source=robinsood_channel&amp;utm_medium=robinsood_channel&amp;utm_campaign=other_challenges_challenges_cost_ever_1405&amp;utm_content=text_cr_260825_040046_ddf1bddc_v1#Tariff</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram channel</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسئول مارکتینگ</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marketing</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-25T04:07:49.043Z</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t xml:space="preserve">UTM-260819-073455-97FF51FF</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t xml:space="preserve">CMP-260819-073228-B8679789</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t xml:space="preserve">کمپین شهریور ماه 1405</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t xml:space="preserve">pro_jazb_shahrivar_1405</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t xml:space="preserve">Telegram</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">telegram</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">referral</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">CR-260819-073428-9CBC6708</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">بنر 100 میلیون جایزه رایگان</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.robinsood.com/Challenges?utm_source=telegram&amp;utm_medium=referral&amp;utm_campaign=pro_jazb_shahrivar_1405&amp;utm_content=banner_cr_260819_073428_9cbc6708_v1</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="P24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t xml:space="preserve">مدیر اصلی</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t xml:space="preserve">owner</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19T07:34:55.231Z</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t xml:space="preserve">deleted</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4519,7 +4631,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:27:13.341742+00:00</t>
+          <t xml:space="preserve">2026-09-08T11:28:01.466096+00:00</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4643,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4655,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
     </row>
